--- a/xls/square_eigen_20_quad4_19_un.xlsx
+++ b/xls/square_eigen_20_quad4_19_un.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>type w</t>
   </si>
@@ -72,148 +72,136 @@
     <t>PiecewisePolynomial{:Linear2D}</t>
   </si>
   <si>
-    <t>0.019252009616102846</t>
-  </si>
-  <si>
-    <t>4.8560807562233525e-5</t>
-  </si>
-  <si>
-    <t>0.025676642622257072</t>
-  </si>
-  <si>
-    <t>4.733246903748335e-5</t>
-  </si>
-  <si>
-    <t>0.023921948137313902</t>
-  </si>
-  <si>
-    <t>4.8430252709120884e-5</t>
-  </si>
-  <si>
-    <t>0.01358505916508478</t>
-  </si>
-  <si>
-    <t>37.64680259526017</t>
-  </si>
-  <si>
-    <t>0.006461507358980948</t>
-  </si>
-  <si>
-    <t>27.842694648598258</t>
-  </si>
-  <si>
-    <t>0.012073605813414894</t>
-  </si>
-  <si>
-    <t>19.09154291749248</t>
-  </si>
-  <si>
-    <t>0.16280039729312384</t>
-  </si>
-  <si>
-    <t>6.8520356433326555</t>
-  </si>
-  <si>
-    <t>0.3357309828501591</t>
-  </si>
-  <si>
-    <t>3.402273532301495</t>
-  </si>
-  <si>
-    <t>0.5676075352292841</t>
-  </si>
-  <si>
-    <t>1.3837064839219622</t>
-  </si>
-  <si>
-    <t>1.2809324996612255</t>
-  </si>
-  <si>
-    <t>1.1973942880048316</t>
-  </si>
-  <si>
-    <t>1.1408730052726948</t>
-  </si>
-  <si>
-    <t>14.06136572708712</t>
-  </si>
-  <si>
-    <t>1.6398024930892858</t>
-  </si>
-  <si>
-    <t>0.06849422521127255</t>
-  </si>
-  <si>
-    <t>2.4254049314530564</t>
-  </si>
-  <si>
-    <t>0.026104910645236745</t>
-  </si>
-  <si>
-    <t>3.057824833540471</t>
-  </si>
-  <si>
-    <t>0.0014653755229749794</t>
-  </si>
-  <si>
-    <t>2.445531984771083</t>
-  </si>
-  <si>
-    <t>0.01893838376137772</t>
-  </si>
-  <si>
-    <t>3.822974400389134</t>
-  </si>
-  <si>
-    <t>0.05748019248502231</t>
-  </si>
-  <si>
-    <t>3.946057904146426</t>
-  </si>
-  <si>
-    <t>0.09424476594155126</t>
-  </si>
-  <si>
-    <t>3.8874755856806407</t>
-  </si>
-  <si>
-    <t>0.11793587383632609</t>
-  </si>
-  <si>
-    <t>3.555525063644036</t>
-  </si>
-  <si>
-    <t>0.1543172313200318</t>
-  </si>
-  <si>
-    <t>5.11756607276002</t>
-  </si>
-  <si>
-    <t>0.17025218810795467</t>
-  </si>
-  <si>
-    <t>5.330766309993793</t>
-  </si>
-  <si>
-    <t>0.15960041573888564</t>
-  </si>
-  <si>
-    <t>5.706099388238732</t>
-  </si>
-  <si>
-    <t>0.18644417179708642</t>
-  </si>
-  <si>
-    <t>5.80094293534611</t>
-  </si>
-  <si>
-    <t>0.17883180763573792</t>
-  </si>
-  <si>
-    <t>5.741626340398349</t>
-  </si>
-  <si>
-    <t>0.16377742617894497</t>
+    <t>0.03520866181615866</t>
+  </si>
+  <si>
+    <t>4.793933068847292e-5</t>
+  </si>
+  <si>
+    <t>0.01116795691716534</t>
+  </si>
+  <si>
+    <t>4.744947572326255e-5</t>
+  </si>
+  <si>
+    <t>0.0071947642805375595</t>
+  </si>
+  <si>
+    <t>4.715088816409616e-5</t>
+  </si>
+  <si>
+    <t>0.010157562438009736</t>
+  </si>
+  <si>
+    <t>4.720001858867752e-5</t>
+  </si>
+  <si>
+    <t>0.012761921548275972</t>
+  </si>
+  <si>
+    <t>5.0565054423828394e-5</t>
+  </si>
+  <si>
+    <t>0.038130186305380606</t>
+  </si>
+  <si>
+    <t>5.078350855626017e-5</t>
+  </si>
+  <si>
+    <t>0.19896054848635764</t>
+  </si>
+  <si>
+    <t>5.2641289691161785e-5</t>
+  </si>
+  <si>
+    <t>0.17853481571922447</t>
+  </si>
+  <si>
+    <t>4.8994274396964466e-5</t>
+  </si>
+  <si>
+    <t>0.8821039695308691</t>
+  </si>
+  <si>
+    <t>16.807543137409787</t>
+  </si>
+  <si>
+    <t>0.6886531185890152</t>
+  </si>
+  <si>
+    <t>21.75344935071779</t>
+  </si>
+  <si>
+    <t>1.7455693993488306</t>
+  </si>
+  <si>
+    <t>25.441631565818543</t>
+  </si>
+  <si>
+    <t>1.8690809573113283</t>
+  </si>
+  <si>
+    <t>3.285499458486049</t>
+  </si>
+  <si>
+    <t>1.5504692318583175</t>
+  </si>
+  <si>
+    <t>2.940689874373762</t>
+  </si>
+  <si>
+    <t>1.738731024866328</t>
+  </si>
+  <si>
+    <t>0.008079963624977893</t>
+  </si>
+  <si>
+    <t>2.125275593068188</t>
+  </si>
+  <si>
+    <t>0.1058039483632273</t>
+  </si>
+  <si>
+    <t>2.5604604400325894</t>
+  </si>
+  <si>
+    <t>1.4854315089937065</t>
+  </si>
+  <si>
+    <t>1.676768643959461</t>
+  </si>
+  <si>
+    <t>1.0341460449593316</t>
+  </si>
+  <si>
+    <t>3.5526465983877533</t>
+  </si>
+  <si>
+    <t>1.9507945185336282</t>
+  </si>
+  <si>
+    <t>1.682250258826928</t>
+  </si>
+  <si>
+    <t>2.475351307494884</t>
+  </si>
+  <si>
+    <t>3.9091504814702747</t>
+  </si>
+  <si>
+    <t>2.6447024041340845</t>
+  </si>
+  <si>
+    <t>3.518667383323879</t>
+  </si>
+  <si>
+    <t>1.8037597596813015</t>
+  </si>
+  <si>
+    <t>5.365599807818149</t>
+  </si>
+  <si>
+    <t>3.567237255585682</t>
   </si>
 </sst>
 </file>
@@ -565,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -611,25 +599,25 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
@@ -638,10 +626,10 @@
         <v>16</v>
       </c>
       <c r="K10">
-        <v>-1.7155239300707563</v>
+        <v>-1.4533504809480544</v>
       </c>
       <c r="L10">
-        <v>-4.313714099591251</v>
+        <v>-4.3193080337218905</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -649,25 +637,25 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11">
-        <v>549</v>
+        <v>420</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -676,10 +664,10 @@
         <v>18</v>
       </c>
       <c r="K11">
-        <v>-1.5904617635451777</v>
+        <v>-1.9520262701035653</v>
       </c>
       <c r="L11">
-        <v>-4.324840840527002</v>
+        <v>-4.323768581798373</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -687,25 +675,25 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
       <c r="F12">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
       <c r="H12">
-        <v>675</v>
+        <v>549</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
@@ -714,10 +702,10 @@
         <v>20</v>
       </c>
       <c r="K12">
-        <v>-1.6212034555016086</v>
+        <v>-2.1429834301274844</v>
       </c>
       <c r="L12">
-        <v>-4.314883264798383</v>
+        <v>-4.326510122202728</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -725,25 +713,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13">
-        <v>330</v>
+        <v>212</v>
       </c>
       <c r="G13" t="s">
         <v>14</v>
       </c>
       <c r="H13">
-        <v>891</v>
+        <v>561</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -752,10 +740,10 @@
         <v>22</v>
       </c>
       <c r="K13">
-        <v>-1.866938465820703</v>
+        <v>-1.9932104994076796</v>
       </c>
       <c r="L13">
-        <v>1.5757280967597755</v>
+        <v>-4.326057830328656</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -763,25 +751,25 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
       </c>
       <c r="F14">
-        <v>424</v>
+        <v>254</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
       </c>
       <c r="H14">
-        <v>1161</v>
+        <v>675</v>
       </c>
       <c r="I14" t="s">
         <v>23</v>
@@ -790,10 +778,10 @@
         <v>24</v>
       </c>
       <c r="K14">
-        <v>-2.1896661567225855</v>
+        <v>-1.8940839294562668</v>
       </c>
       <c r="L14">
-        <v>1.4447112645012028</v>
+        <v>-4.2961495209862735</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -801,25 +789,25 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
       <c r="D15">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
       </c>
       <c r="F15">
-        <v>556</v>
+        <v>285</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
       <c r="H15">
-        <v>1545</v>
+        <v>768</v>
       </c>
       <c r="I15" t="s">
         <v>25</v>
@@ -828,10 +816,10 @@
         <v>26</v>
       </c>
       <c r="K15">
-        <v>-1.9181630073672014</v>
+        <v>-1.4187310727436104</v>
       </c>
       <c r="L15">
-        <v>1.2808410281042693</v>
+        <v>-4.294277297672904</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -839,25 +827,25 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
       </c>
       <c r="F16">
-        <v>657</v>
+        <v>330</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
       <c r="H16">
-        <v>1836</v>
+        <v>891</v>
       </c>
       <c r="I16" t="s">
         <v>27</v>
@@ -866,10 +854,10 @@
         <v>28</v>
       </c>
       <c r="K16">
-        <v>-0.7883445396065175</v>
+        <v>-0.7012330304910849</v>
       </c>
       <c r="L16">
-        <v>0.8358196134386023</v>
+        <v>-4.27867347921755</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -877,25 +865,25 @@
         <v>12</v>
       </c>
       <c r="B17">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
       </c>
       <c r="F17">
-        <v>781</v>
+        <v>365</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
       <c r="H17">
-        <v>2196</v>
+        <v>996</v>
       </c>
       <c r="I17" t="s">
         <v>29</v>
@@ -904,10 +892,10 @@
         <v>30</v>
       </c>
       <c r="K17">
-        <v>-0.4740085781444166</v>
+        <v>-0.7482770803901102</v>
       </c>
       <c r="L17">
-        <v>0.5317692266174424</v>
+        <v>-4.309854669830537</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -915,25 +903,25 @@
         <v>12</v>
       </c>
       <c r="B18">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="D18">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
       </c>
       <c r="F18">
-        <v>899</v>
+        <v>424</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18">
-        <v>2538</v>
+        <v>1161</v>
       </c>
       <c r="I18" t="s">
         <v>31</v>
@@ -942,10 +930,10 @@
         <v>32</v>
       </c>
       <c r="K18">
-        <v>-0.24595184773398593</v>
+        <v>-0.05448022356157399</v>
       </c>
       <c r="L18">
-        <v>0.1410439760080178</v>
+        <v>1.2255042345669513</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -953,25 +941,25 @@
         <v>12</v>
       </c>
       <c r="B19">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
       </c>
       <c r="F19">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19">
-        <v>2853</v>
+        <v>1275</v>
       </c>
       <c r="I19" t="s">
         <v>33</v>
@@ -980,10 +968,10 @@
         <v>34</v>
       </c>
       <c r="K19">
-        <v>0.10752624465722437</v>
+        <v>-0.1619994814565468</v>
       </c>
       <c r="L19">
-        <v>0.07823718207599378</v>
+        <v>1.3375281309554015</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -991,25 +979,25 @@
         <v>12</v>
       </c>
       <c r="B20">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
       </c>
       <c r="F20">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
       <c r="H20">
-        <v>3264</v>
+        <v>1545</v>
       </c>
       <c r="I20" t="s">
         <v>35</v>
@@ -1018,10 +1006,10 @@
         <v>36</v>
       </c>
       <c r="K20">
-        <v>0.05723730420889626</v>
+        <v>0.24193711992481653</v>
       </c>
       <c r="L20">
-        <v>1.1480275041071812</v>
+        <v>1.405544959071928</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1029,25 +1017,25 @@
         <v>12</v>
       </c>
       <c r="B21">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
       </c>
       <c r="F21">
-        <v>1295</v>
+        <v>649</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
       </c>
       <c r="H21">
-        <v>3690</v>
+        <v>1812</v>
       </c>
       <c r="I21" t="s">
         <v>37</v>
@@ -1056,10 +1044,10 @@
         <v>38</v>
       </c>
       <c r="K21">
-        <v>0.21479154236054426</v>
+        <v>0.27162811280318944</v>
       </c>
       <c r="L21">
-        <v>-1.1643460425893155</v>
+        <v>0.5166013999463971</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1067,25 +1055,25 @@
         <v>12</v>
       </c>
       <c r="B22">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="D22">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E22" t="s">
         <v>13</v>
       </c>
       <c r="F22">
-        <v>1450</v>
+        <v>657</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22">
-        <v>4143</v>
+        <v>1836</v>
       </c>
       <c r="I22" t="s">
         <v>39</v>
@@ -1094,10 +1082,10 @@
         <v>40</v>
       </c>
       <c r="K22">
-        <v>0.3847842562638729</v>
+        <v>0.19046315234262284</v>
       </c>
       <c r="L22">
-        <v>-1.5832777890017058</v>
+        <v>0.4684492261561962</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1105,25 +1093,25 @@
         <v>12</v>
       </c>
       <c r="B23">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
       </c>
       <c r="F23">
-        <v>1625</v>
+        <v>781</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
       </c>
       <c r="H23">
-        <v>4656</v>
+        <v>2196</v>
       </c>
       <c r="I23" t="s">
         <v>41</v>
@@ -1132,10 +1120,10 @@
         <v>42</v>
       </c>
       <c r="K23">
-        <v>0.4854126033766028</v>
+        <v>0.24023240347986485</v>
       </c>
       <c r="L23">
-        <v>-2.8340510670113446</v>
+        <v>-2.0925905943624112</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1143,25 +1131,25 @@
         <v>12</v>
       </c>
       <c r="B24">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="D24">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E24" t="s">
         <v>13</v>
       </c>
       <c r="F24">
-        <v>1827</v>
+        <v>806</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
       </c>
       <c r="H24">
-        <v>5250</v>
+        <v>2271</v>
       </c>
       <c r="I24" t="s">
         <v>43</v>
@@ -1170,10 +1158,10 @@
         <v>44</v>
       </c>
       <c r="K24">
-        <v>0.38837334727128514</v>
+        <v>0.3274152547572389</v>
       </c>
       <c r="L24">
-        <v>-1.7226570872897677</v>
+        <v>-0.9754981251140047</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1181,25 +1169,25 @@
         <v>12</v>
       </c>
       <c r="B25">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="D25">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E25" t="s">
         <v>13</v>
       </c>
       <c r="F25">
-        <v>2033</v>
+        <v>899</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
       </c>
       <c r="H25">
-        <v>5856</v>
+        <v>2538</v>
       </c>
       <c r="I25" t="s">
         <v>45</v>
@@ -1208,10 +1196,10 @@
         <v>46</v>
       </c>
       <c r="K25">
-        <v>0.5824013898822347</v>
+        <v>0.40831807022771865</v>
       </c>
       <c r="L25">
-        <v>-1.2404817862051212</v>
+        <v>0.1718526319378401</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1219,25 +1207,25 @@
         <v>12</v>
       </c>
       <c r="B26">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="D26">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E26" t="s">
         <v>13</v>
       </c>
       <c r="F26">
-        <v>2279</v>
+        <v>940</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26">
-        <v>6582</v>
+        <v>2661</v>
       </c>
       <c r="I26" t="s">
         <v>47</v>
@@ -1246,10 +1234,10 @@
         <v>48</v>
       </c>
       <c r="K26">
-        <v>0.596163453766341</v>
+        <v>0.22447314395182705</v>
       </c>
       <c r="L26">
-        <v>-1.0257427598046325</v>
+        <v>0.014581875354734663</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1257,25 +1245,25 @@
         <v>12</v>
       </c>
       <c r="B27">
+        <v>462</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27">
+        <v>556</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27">
         <v>1008</v>
       </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27">
-        <v>1149</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27">
-        <v>2498</v>
-      </c>
       <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27">
-        <v>7227</v>
+        <v>2853</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1284,10 +1272,10 @@
         <v>50</v>
       </c>
       <c r="K27">
-        <v>0.5896676745654478</v>
+        <v>0.5505520079386338</v>
       </c>
       <c r="L27">
-        <v>-0.9283540707371339</v>
+        <v>0.29021152661301725</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1295,25 +1283,25 @@
         <v>12</v>
       </c>
       <c r="B28">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
       </c>
       <c r="D28">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E28" t="s">
         <v>13</v>
       </c>
       <c r="F28">
-        <v>2737</v>
+        <v>1062</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
       <c r="H28">
-        <v>7932</v>
+        <v>3015</v>
       </c>
       <c r="I28" t="s">
         <v>51</v>
@@ -1322,10 +1310,10 @@
         <v>52</v>
       </c>
       <c r="K28">
-        <v>0.5509037444202284</v>
+        <v>0.22589060379416423</v>
       </c>
       <c r="L28">
-        <v>-0.811585577181298</v>
+        <v>0.39363684370569335</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1333,25 +1321,25 @@
         <v>12</v>
       </c>
       <c r="B29">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
       </c>
       <c r="D29">
+        <v>556</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29">
         <v>1149</v>
       </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29">
-        <v>2918</v>
-      </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
       <c r="H29">
-        <v>8463</v>
+        <v>3264</v>
       </c>
       <c r="I29" t="s">
         <v>53</v>
@@ -1360,10 +1348,10 @@
         <v>54</v>
       </c>
       <c r="K29">
-        <v>0.7090634585352936</v>
+        <v>0.5920823887781863</v>
       </c>
       <c r="L29">
-        <v>-0.7689072977581792</v>
+        <v>0.4223768100143979</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1371,25 +1359,25 @@
         <v>12</v>
       </c>
       <c r="B30">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="D30">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E30" t="s">
         <v>13</v>
       </c>
       <c r="F30">
-        <v>3203</v>
+        <v>1194</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
       </c>
       <c r="H30">
-        <v>9306</v>
+        <v>3399</v>
       </c>
       <c r="I30" t="s">
         <v>55</v>
@@ -1398,10 +1386,10 @@
         <v>56</v>
       </c>
       <c r="K30">
-        <v>0.726789644351131</v>
+        <v>0.546378215282378</v>
       </c>
       <c r="L30">
-        <v>-0.7969659817016503</v>
+        <v>0.25617869396393034</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1409,25 +1397,25 @@
         <v>12</v>
       </c>
       <c r="B31">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
       </c>
       <c r="F31">
-        <v>3411</v>
+        <v>1295</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
       </c>
       <c r="H31">
-        <v>9918</v>
+        <v>3690</v>
       </c>
       <c r="I31" t="s">
         <v>57</v>
@@ -1436,86 +1424,10 @@
         <v>58</v>
       </c>
       <c r="K31">
-        <v>0.7563393318825252</v>
+        <v>0.7296182777772948</v>
       </c>
       <c r="L31">
-        <v>-0.7294511880383997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32">
-        <v>1008</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32">
-        <v>1149</v>
-      </c>
-      <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32">
-        <v>3691</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32">
-        <v>10746</v>
-      </c>
-      <c r="I32" t="s">
-        <v>59</v>
-      </c>
-      <c r="J32" t="s">
-        <v>60</v>
-      </c>
-      <c r="K32">
-        <v>0.763498593275528</v>
-      </c>
-      <c r="L32">
-        <v>-0.747555233570758</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33">
-        <v>1008</v>
-      </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33">
-        <v>1149</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33">
-        <v>3936</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33">
-        <v>11469</v>
-      </c>
-      <c r="I33" t="s">
-        <v>61</v>
-      </c>
-      <c r="J33" t="s">
-        <v>62</v>
-      </c>
-      <c r="K33">
-        <v>0.7590349256067687</v>
-      </c>
-      <c r="L33">
-        <v>-0.7857459582625416</v>
+        <v>0.5523319950588618</v>
       </c>
     </row>
   </sheetData>
